--- a/data/trending_integrated_20261006_15.xlsx
+++ b/data/trending_integrated_20261006_15.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52897858610</v>
+        <v>52914875690</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7010</v>
+        <v>6950</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+27.45%</t>
+          <t>'+26.36%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="H3" t="n">
         <v>1.87</v>
@@ -702,7 +702,7 @@
         <v>1.6</v>
       </c>
       <c r="O3" t="n">
-        <v>118730817750</v>
+        <v>120795903630</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47300</v>
+        <v>47400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.93%</t>
+          <t>'+17.18%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="G4" t="n">
-        <v>4593</v>
+        <v>4599</v>
       </c>
       <c r="H4" t="n">
         <v>14.1</v>
@@ -794,7 +794,7 @@
         <v>14.11</v>
       </c>
       <c r="O4" t="n">
-        <v>257945243300</v>
+        <v>259453287250</v>
       </c>
       <c r="P4" t="n">
         <v>69200</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>리보세라닙 관련 FDA 실사 결과(VAI) 긍정적. 간암 신약 승인 기대감 고조 및 로슈 능가 전망.</t>
+          <t>FDA 실사 VAI 판정 및 HLB의 간암 신약 FDA 승인 기대감에 따른 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['리보세라닙', 'FDA 실사', '간암 신약']</t>
+          <t>['FDA 실사', '간암 신약', '승인 기대감']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17800</v>
+        <v>17770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.89%</t>
+          <t>'+15.69%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.8</v>
       </c>
       <c r="E5" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H5" t="n">
         <v>2.17</v>
@@ -886,7 +886,7 @@
         <v>1.37</v>
       </c>
       <c r="O5" t="n">
-        <v>107546432920</v>
+        <v>108142575690</v>
       </c>
       <c r="P5" t="n">
         <v>38400</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+14.09%</t>
+          <t>'+13.86%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.38</v>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="H6" t="n">
         <v>1.4</v>
@@ -978,7 +978,7 @@
         <v>1.02</v>
       </c>
       <c r="O6" t="n">
-        <v>151288282577</v>
+        <v>153234922932</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3100</v>
+        <v>3095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.96%</t>
+          <t>'+8.79%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.57</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F7" t="n">
         <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="H7" t="n">
         <v>1.82</v>
@@ -1070,7 +1070,7 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>53885543214</v>
+        <v>54167353659</v>
       </c>
       <c r="P7" t="n">
         <v>4810</v>
@@ -1130,13 +1130,13 @@
         <v>0.21</v>
       </c>
       <c r="E8" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G8" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
@@ -1162,7 +1162,7 @@
         <v>0.83</v>
       </c>
       <c r="O8" t="n">
-        <v>145927631715</v>
+        <v>146513351865</v>
       </c>
       <c r="P8" t="n">
         <v>30550</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.13%</t>
+          <t>'+8.06%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H9" t="n">
         <v>1.09</v>
@@ -1254,7 +1254,7 @@
         <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>20634185861</v>
+        <v>20765187880</v>
       </c>
       <c r="P9" t="n">
         <v>2970</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18550</v>
+        <v>18530</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.21%</t>
+          <t>'+4.10%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G10" t="n">
-        <v>873</v>
+        <v>912</v>
       </c>
       <c r="H10" t="n">
         <v>3.81</v>
@@ -1346,7 +1346,7 @@
         <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>231207997765</v>
+        <v>233772629360</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시 광통신 섹터 강세 및 국내 3분기 영업이익 증가. 전고점 돌파 및 매물 소화 과정 분석.</t>
+          <t>미국 증시 광통신 섹터 강세와 함께 대한광통신의 3분기 영업이익 증가, 수급 개선 및 상승 추세 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '영업이익', '전고점']</t>
+          <t>['광통신', '영업이익', '수급 개선']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1412,7 +1412,7 @@
         <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H11" t="n">
         <v>9.390000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>62712785700</v>
+        <v>63638444435</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>272250</v>
+        <v>19640</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.36%</t>
+          <t>'-1.60%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>112</v>
       </c>
       <c r="F12" t="n">
-        <v>448</v>
+        <v>74</v>
       </c>
       <c r="G12" t="n">
-        <v>1607</v>
+        <v>321</v>
       </c>
       <c r="H12" t="n">
-        <v>46.41</v>
+        <v>27.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,91 +1515,91 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>276000</v>
+        <v>19960</v>
       </c>
       <c r="K12" t="n">
-        <v>278500</v>
+        <v>20150</v>
       </c>
       <c r="L12" t="n">
-        <v>279000</v>
+        <v>20150</v>
       </c>
       <c r="M12" t="n">
-        <v>270000</v>
+        <v>19600</v>
       </c>
       <c r="N12" t="n">
-        <v>46.41</v>
+        <v>27.73</v>
       </c>
       <c r="O12" t="n">
-        <v>2839513927250</v>
+        <v>42336857935</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>90200</v>
+        <v>18440</v>
       </c>
       <c r="R12" t="n">
-        <v>-1469000</v>
+        <v>-642000</v>
       </c>
       <c r="S12" t="n">
-        <v>139000</v>
+        <v>-47000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>영업이익 100조 예상에도 불구하고 주가 하락세 지속. 정치적 이슈와 자사주 매입 정책에 대한 불만 제기. 향후 3분기 실적 및 주가 추이 불확실.</t>
+          <t>수주 기대감에도 불구하고 주가 부진에 대한 답답함과 불신 드러남.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '주가', '실적']</t>
+          <t>['수주', '조선주', '주가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19650</v>
+        <v>271500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.55%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>111</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>448</v>
       </c>
       <c r="G13" t="n">
-        <v>317</v>
+        <v>1630</v>
       </c>
       <c r="H13" t="n">
-        <v>27.78</v>
+        <v>46.41</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,60 +1607,60 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>19960</v>
+        <v>276000</v>
       </c>
       <c r="K13" t="n">
-        <v>20150</v>
+        <v>278500</v>
       </c>
       <c r="L13" t="n">
-        <v>20150</v>
+        <v>279000</v>
       </c>
       <c r="M13" t="n">
-        <v>19600</v>
+        <v>270000</v>
       </c>
       <c r="N13" t="n">
-        <v>27.73</v>
+        <v>46.41</v>
       </c>
       <c r="O13" t="n">
-        <v>41365516540</v>
+        <v>2919319443250</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>18440</v>
+        <v>90200</v>
       </c>
       <c r="R13" t="n">
-        <v>-642000</v>
+        <v>-1469000</v>
       </c>
       <c r="S13" t="n">
-        <v>-47000</v>
+        <v>139000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>수주 기대감에도 불구하고 주가 부진에 대한 답답함과 불신 드러남.</t>
+          <t>영업이익 100조 예상에도 불구하고 주가 부진, 정치적 요인 및 자사주 매입 정책에 대한 부정적 의견.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주', '조선주', '주가']</t>
+          <t>['영업이익', '자사주 매입', '주가 부진']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1785000</v>
+        <v>1779000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.04%</t>
+          <t>'-3.37%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G14" t="n">
-        <v>1950</v>
+        <v>1966</v>
       </c>
       <c r="H14" t="n">
         <v>49.76</v>
@@ -1714,7 +1714,7 @@
         <v>49.77</v>
       </c>
       <c r="O14" t="n">
-        <v>3938784416000</v>
+        <v>4068555348500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 리스크 및 국민연금 운용에 대한 비판 제기. 반도체 산업 전반의 부진과 더불어 SK하이닉스 주가 하락에 대한 부정적 전망. 주가 조작 의혹 및 정치적 이슈 연관성 시사.</t>
+          <t>이재명 리스크 및 정치적 요인이 주가에 부정적 영향을 미치고 있다는 의견.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['정치적 리스크', '주가 하락', '반도체']</t>
+          <t>['이재명 리스크', '정치적 요인', '주가 조작']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14700</v>
+        <v>14660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.23%</t>
+          <t>'-4.50%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.14</v>
       </c>
       <c r="E15" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G15" t="n">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="H15" t="n">
         <v>0.32</v>
@@ -1806,7 +1806,7 @@
         <v>0.18</v>
       </c>
       <c r="O15" t="n">
-        <v>73893176260</v>
+        <v>74649063285</v>
       </c>
       <c r="P15" t="n">
         <v>29750</v>

--- a/data/trending_integrated_20261006_15.xlsx
+++ b/data/trending_integrated_20261006_15.xlsx
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52914875690</v>
+        <v>52924607170</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6950</v>
+        <v>6970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+26.36%</t>
+          <t>'+26.73%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G3" t="n">
         <v>155</v>
@@ -702,7 +702,7 @@
         <v>1.6</v>
       </c>
       <c r="O3" t="n">
-        <v>120795903630</v>
+        <v>122367295600</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G4" t="n">
-        <v>4599</v>
+        <v>4666</v>
       </c>
       <c r="H4" t="n">
         <v>14.1</v>
@@ -794,7 +794,7 @@
         <v>14.11</v>
       </c>
       <c r="O4" t="n">
-        <v>259453287250</v>
+        <v>261231758850</v>
       </c>
       <c r="P4" t="n">
         <v>69200</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17770</v>
+        <v>17830</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.69%</t>
+          <t>'+16.08%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -886,7 +886,7 @@
         <v>1.37</v>
       </c>
       <c r="O5" t="n">
-        <v>108142575690</v>
+        <v>108936935700</v>
       </c>
       <c r="P5" t="n">
         <v>38400</v>
@@ -946,13 +946,13 @@
         <v>0.38</v>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G6" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H6" t="n">
         <v>1.4</v>
@@ -978,7 +978,7 @@
         <v>1.02</v>
       </c>
       <c r="O6" t="n">
-        <v>153234922932</v>
+        <v>155342360070</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3095</v>
+        <v>20450</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.79%</t>
+          <t>'+8.83%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.57</v>
+        <v>0.21</v>
       </c>
       <c r="E7" t="n">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="G7" t="n">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="H7" t="n">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2845</v>
+        <v>18790</v>
       </c>
       <c r="K7" t="n">
-        <v>3200</v>
+        <v>21400</v>
       </c>
       <c r="L7" t="n">
-        <v>3360</v>
+        <v>22300</v>
       </c>
       <c r="M7" t="n">
-        <v>2995</v>
+        <v>20050</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="O7" t="n">
-        <v>54167353659</v>
+        <v>147404826565</v>
       </c>
       <c r="P7" t="n">
-        <v>4810</v>
+        <v>30550</v>
       </c>
       <c r="Q7" t="n">
-        <v>1400</v>
+        <v>6100</v>
       </c>
       <c r="R7" t="n">
-        <v>130000</v>
+        <v>-58000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
+          <t>보안주로서 연말 기대감 및 신규 기술(양자 보안) 관련 긍정적 전망. 은행권 해킹 이슈와 연계된 보안주 상승 가능성 언급. 차익 실현 매물 및 기관 매수세 유입 관찰.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['CB', '차익실현', '공매도']</t>
+          <t>['보안주', '양자 보안', '상승 기대']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,43 +1103,43 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20350</v>
+        <v>3090</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.30%</t>
+          <t>'+8.61%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.21</v>
+        <v>0.57</v>
       </c>
       <c r="E8" t="n">
-        <v>135</v>
+        <v>64</v>
       </c>
       <c r="F8" t="n">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18790</v>
+        <v>2845</v>
       </c>
       <c r="K8" t="n">
-        <v>21400</v>
+        <v>3200</v>
       </c>
       <c r="L8" t="n">
-        <v>22300</v>
+        <v>3360</v>
       </c>
       <c r="M8" t="n">
-        <v>20050</v>
+        <v>2995</v>
       </c>
       <c r="N8" t="n">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>146513351865</v>
+        <v>54444670869</v>
       </c>
       <c r="P8" t="n">
-        <v>30550</v>
+        <v>4810</v>
       </c>
       <c r="Q8" t="n">
-        <v>6100</v>
+        <v>1400</v>
       </c>
       <c r="R8" t="n">
-        <v>-58000</v>
+        <v>130000</v>
       </c>
       <c r="S8" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>보안주로서 연말 기대감 및 신규 기술(양자 보안) 관련 긍정적 전망. 은행권 해킹 이슈와 연계된 보안주 상승 가능성 언급. 차익 실현 매물 및 기관 매수세 유입 관찰.</t>
+          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보안주', '양자 보안', '상승 기대']</t>
+          <t>['CB', '차익실현', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.06%</t>
+          <t>'+8.28%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.17</v>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F9" t="n">
         <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H9" t="n">
         <v>1.09</v>
@@ -1254,7 +1254,7 @@
         <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>20765187880</v>
+        <v>20912945470</v>
       </c>
       <c r="P9" t="n">
         <v>2970</v>
@@ -1314,13 +1314,13 @@
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F10" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G10" t="n">
-        <v>912</v>
+        <v>931</v>
       </c>
       <c r="H10" t="n">
         <v>3.81</v>
@@ -1346,7 +1346,7 @@
         <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>233772629360</v>
+        <v>235806362130</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시 광통신 섹터 강세와 함께 대한광통신의 3분기 영업이익 증가, 수급 개선 및 상승 추세 전망.</t>
+          <t>대한광통신, 미국 증시 광통신 섹터 강세와 함께 3분기 영업이익 증가. 목표가 상향 및 외인 순매수 기반 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '영업이익', '수급 개선']</t>
+          <t>['광통신', '영업이익', '외인 순매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17690</v>
+        <v>17730</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.45%</t>
+          <t>'+0.68%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1438,7 +1438,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>63638444435</v>
+        <v>64892795750</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19640</v>
+        <v>19680</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.60%</t>
+          <t>'-1.40%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G12" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="H12" t="n">
         <v>27.78</v>
@@ -1530,7 +1530,7 @@
         <v>27.73</v>
       </c>
       <c r="O12" t="n">
-        <v>42336857935</v>
+        <v>43788846920</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>271500</v>
+        <v>272000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-1.45%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G13" t="n">
-        <v>1630</v>
+        <v>1603</v>
       </c>
       <c r="H13" t="n">
         <v>46.41</v>
@@ -1622,7 +1622,7 @@
         <v>46.41</v>
       </c>
       <c r="O13" t="n">
-        <v>2919319443250</v>
+        <v>3081042148750</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>영업이익 100조 예상에도 불구하고 주가 부진, 정치적 요인 및 자사주 매입 정책에 대한 부정적 의견.</t>
+          <t>삼성전자, 110조 영업이익 예상에도 주가 부진 지속. 정치적 이슈와 자사주 매입 관련 부정적 언급 다수.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['영업이익', '자사주 매입', '주가 부진']</t>
+          <t>['영업이익', '자사주 매입', '정치']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779000</v>
+        <v>1776000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.37%</t>
+          <t>'-3.53%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="G14" t="n">
-        <v>1966</v>
+        <v>1973</v>
       </c>
       <c r="H14" t="n">
         <v>49.76</v>
@@ -1714,7 +1714,7 @@
         <v>49.77</v>
       </c>
       <c r="O14" t="n">
-        <v>4068555348500</v>
+        <v>4173208786500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>이재명 리스크 및 정치적 요인이 주가에 부정적 영향을 미치고 있다는 의견.</t>
+          <t>SK하이닉스, 정치적 리스크와 주가 조작 의혹 제기. 최근 상승분 반납하며 부진한 흐름.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['이재명 리스크', '정치적 요인', '주가 조작']</t>
+          <t>['정치 리스크', '주가 조작', '폭락']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14660</v>
+        <v>14710</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.50%</t>
+          <t>'-4.17%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.14</v>
       </c>
       <c r="E15" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G15" t="n">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="H15" t="n">
         <v>0.32</v>
@@ -1806,7 +1806,7 @@
         <v>0.18</v>
       </c>
       <c r="O15" t="n">
-        <v>74649063285</v>
+        <v>75361533690</v>
       </c>
       <c r="P15" t="n">
         <v>29750</v>

--- a/data/trending_integrated_20261006_15.xlsx
+++ b/data/trending_integrated_20261006_15.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52924607170</v>
+        <v>52989813290</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6970</v>
+        <v>6980</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+26.73%</t>
+          <t>'+26.91%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F3" t="n">
         <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H3" t="n">
         <v>1.87</v>
@@ -702,7 +702,7 @@
         <v>1.6</v>
       </c>
       <c r="O3" t="n">
-        <v>122367295600</v>
+        <v>122774822900</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>양자암호, 보안 기업으로서의 잠재력 언급. 해킹 방어 및 우리은행 협력 사례 제시. 단기 변동성에 대한 의견도 존재.</t>
+          <t>양자암호 및 보안 기술 관련 기업으로 언급되며, 향후 성장 가능성에 대한 기대감 표출. 해킹 방어 능력과 목표 주가 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자암호', '해킹 방어', '보안']</t>
+          <t>['양자암호', '보안', '목표주가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G4" t="n">
-        <v>4666</v>
+        <v>4635</v>
       </c>
       <c r="H4" t="n">
         <v>14.1</v>
@@ -794,7 +794,7 @@
         <v>14.11</v>
       </c>
       <c r="O4" t="n">
-        <v>261231758850</v>
+        <v>263296265850</v>
       </c>
       <c r="P4" t="n">
         <v>69200</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>FDA 실사 VAI 판정 및 HLB의 간암 신약 FDA 승인 기대감에 따른 주가 상승 전망.</t>
+          <t>HLB의 간암 신약 FDA 실사 결과 및 승인 기대감을 바탕으로 강력한 상승 전망 제시. 공매도 세력에 대한 경고와 함께 목표 주가 및 상승 모멘텀 강조.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['FDA 실사', '간암 신약', '승인 기대감']</t>
+          <t>['간암 신약', 'FDA 실사', '상승 전망']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17830</v>
+        <v>17850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+16.08%</t>
+          <t>'+16.21%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -886,7 +886,7 @@
         <v>1.37</v>
       </c>
       <c r="O5" t="n">
-        <v>108936935700</v>
+        <v>109239707400</v>
       </c>
       <c r="P5" t="n">
         <v>38400</v>
@@ -946,13 +946,13 @@
         <v>0.38</v>
       </c>
       <c r="E6" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H6" t="n">
         <v>1.4</v>
@@ -978,7 +978,7 @@
         <v>1.02</v>
       </c>
       <c r="O6" t="n">
-        <v>155342360070</v>
+        <v>156141660480</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20450</v>
+        <v>20500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.83%</t>
+          <t>'+9.10%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.21</v>
       </c>
       <c r="E7" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F7" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G7" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H7" t="n">
         <v>1.04</v>
@@ -1070,7 +1070,7 @@
         <v>0.83</v>
       </c>
       <c r="O7" t="n">
-        <v>147404826565</v>
+        <v>148037128565</v>
       </c>
       <c r="P7" t="n">
         <v>30550</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>보안주로서 연말 기대감 및 신규 기술(양자 보안) 관련 긍정적 전망. 은행권 해킹 이슈와 연계된 보안주 상승 가능성 언급. 차익 실현 매물 및 기관 매수세 유입 관찰.</t>
+          <t>은행권 보안 위협에 따른 보안주 관심 증대 속에서 엑스게이트의 상승 가능성 언급. 연말 목표 주가 및 잠재적 성장성 제시.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안주', '양자 보안', '상승 기대']</t>
+          <t>['보안주', '은행 해킹', '연말 전망']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3090</v>
+        <v>3095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.61%</t>
+          <t>'+8.79%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.57</v>
       </c>
       <c r="E8" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F8" t="n">
         <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="H8" t="n">
         <v>1.82</v>
@@ -1162,7 +1162,7 @@
         <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>54444670869</v>
+        <v>54564735204</v>
       </c>
       <c r="P8" t="n">
         <v>4810</v>
@@ -1228,7 +1228,7 @@
         <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="H9" t="n">
         <v>1.09</v>
@@ -1254,7 +1254,7 @@
         <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>20912945470</v>
+        <v>20985879985</v>
       </c>
       <c r="P9" t="n">
         <v>2970</v>
@@ -1314,13 +1314,13 @@
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F10" t="n">
         <v>88</v>
       </c>
       <c r="G10" t="n">
-        <v>931</v>
+        <v>942</v>
       </c>
       <c r="H10" t="n">
         <v>3.81</v>
@@ -1346,7 +1346,7 @@
         <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>235806362130</v>
+        <v>236955778030</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대한광통신, 미국 증시 광통신 섹터 강세와 함께 3분기 영업이익 증가. 목표가 상향 및 외인 순매수 기반 상승 기대.</t>
+          <t>미국 증시의 강력한 광통신 섹터 흐름에 기반한 긍정적 전망 제시. 3분기 영업이익 증가 및 외인 순매수 동향을 근거로 상승 추세 예상.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17730</v>
+        <v>17750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.68%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
         <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="H11" t="n">
         <v>9.390000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>64892795750</v>
+        <v>65916757750</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19680</v>
+        <v>19700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.40%</t>
+          <t>'-1.30%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F12" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G12" t="n">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="H12" t="n">
         <v>27.78</v>
@@ -1530,7 +1530,7 @@
         <v>27.73</v>
       </c>
       <c r="O12" t="n">
-        <v>43788846920</v>
+        <v>48606619820</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1596,7 +1596,7 @@
         <v>446</v>
       </c>
       <c r="G13" t="n">
-        <v>1603</v>
+        <v>1640</v>
       </c>
       <c r="H13" t="n">
         <v>46.41</v>
@@ -1622,7 +1622,7 @@
         <v>46.41</v>
       </c>
       <c r="O13" t="n">
-        <v>3081042148750</v>
+        <v>3469186692750</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>삼성전자, 110조 영업이익 예상에도 주가 부진 지속. 정치적 이슈와 자사주 매입 관련 부정적 언급 다수.</t>
+          <t>증시 전반의 불안정한 흐름 속에서 3분기 110조 영업이익 예상에도 불구하고 주가 하락에 대한 불만 표출. 자사주 매입 및 정치적 이슈 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['영업이익', '자사주 매입', '정치']</t>
+          <t>['영업이익', '자사주 매입', '주가 하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1776000</v>
+        <v>1773000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.53%</t>
+          <t>'-3.69%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="G14" t="n">
-        <v>1973</v>
+        <v>2035</v>
       </c>
       <c r="H14" t="n">
         <v>49.76</v>
@@ -1714,7 +1714,7 @@
         <v>49.77</v>
       </c>
       <c r="O14" t="n">
-        <v>4173208786500</v>
+        <v>4740625522500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>SK하이닉스, 정치적 리스크와 주가 조작 의혹 제기. 최근 상승분 반납하며 부진한 흐름.</t>
+          <t>정치적 리스크 및 시장 수급 불안정성을 근거로 주가 급락에 대한 강한 불만과 부정적 전망 제시. 주가 조작 의혹 및 국내 증시 소외감 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['정치 리스크', '주가 조작', '폭락']</t>
+          <t>['이재명 리스크', '주가 조작', '수급 불안정']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14710</v>
+        <v>14700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.17%</t>
+          <t>'-4.23%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.14</v>
       </c>
       <c r="E15" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F15" t="n">
         <v>64</v>
       </c>
       <c r="G15" t="n">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="H15" t="n">
         <v>0.32</v>
@@ -1806,7 +1806,7 @@
         <v>0.18</v>
       </c>
       <c r="O15" t="n">
-        <v>75361533690</v>
+        <v>75491334690</v>
       </c>
       <c r="P15" t="n">
         <v>29750</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집에 따른 주가 상승 기대감 있으나, 구체적인 호재는 부족.</t>
+          <t>기타법인의 자사주 매집을 근거로 한 초저평가 및 상승 기대감 표출. 다만, 주가 상승 탄력에 대한 의문 및 단기적 흐름에 대한 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['자사주', '매집', '주가']</t>
+          <t>['자사주 매집', '초저평가', '수급']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261006_15.xlsx
+++ b/data/trending_integrated_20261006_15.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G2" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -676,7 +676,7 @@
         <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H3" t="n">
         <v>1.87</v>
@@ -702,7 +702,7 @@
         <v>1.6</v>
       </c>
       <c r="O3" t="n">
-        <v>122774822900</v>
+        <v>122798303620</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>양자암호 및 보안 기술 관련 기업으로 언급되며, 향후 성장 가능성에 대한 기대감 표출. 해킹 방어 능력과 목표 주가 제시.</t>
+          <t>양자암호 및 보안 기술에 대한 기대감과 함께 급등세를 보임. 해킹 방어 능력과 AI 보안 관련 긍정적 언급이 있으며, 목표 주가 상향 조정 등 투자 심리가 호전됨.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자암호', '보안', '목표주가']</t>
+          <t>['양자암호', 'AI 보안', '목표 주가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="G4" t="n">
-        <v>4635</v>
+        <v>4713</v>
       </c>
       <c r="H4" t="n">
         <v>14.1</v>
@@ -794,7 +794,7 @@
         <v>14.11</v>
       </c>
       <c r="O4" t="n">
-        <v>263296265850</v>
+        <v>263319491850</v>
       </c>
       <c r="P4" t="n">
         <v>69200</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>HLB의 간암 신약 FDA 실사 결과 및 승인 기대감을 바탕으로 강력한 상승 전망 제시. 공매도 세력에 대한 경고와 함께 목표 주가 및 상승 모멘텀 강조.</t>
+          <t>FDA 실사 VAI 판정 및 HLB의 간암 신약 FDA 승인 기대감에 따른 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['간암 신약', 'FDA 실사', '상승 전망']</t>
+          <t>['FDA 실사', '간암 신약', '승인 기대감']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -886,7 +886,7 @@
         <v>1.37</v>
       </c>
       <c r="O5" t="n">
-        <v>109239707400</v>
+        <v>109246490400</v>
       </c>
       <c r="P5" t="n">
         <v>38400</v>
@@ -946,13 +946,13 @@
         <v>0.38</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H6" t="n">
         <v>1.4</v>
@@ -978,7 +978,7 @@
         <v>1.02</v>
       </c>
       <c r="O6" t="n">
-        <v>156141660480</v>
+        <v>156218699250</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -1038,10 +1038,10 @@
         <v>0.21</v>
       </c>
       <c r="E7" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F7" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G7" t="n">
         <v>225</v>
@@ -1070,7 +1070,7 @@
         <v>0.83</v>
       </c>
       <c r="O7" t="n">
-        <v>148037128565</v>
+        <v>148061175065</v>
       </c>
       <c r="P7" t="n">
         <v>30550</v>
@@ -1130,13 +1130,13 @@
         <v>0.57</v>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
         <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H8" t="n">
         <v>1.82</v>
@@ -1162,7 +1162,7 @@
         <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>54564735204</v>
+        <v>54571426594</v>
       </c>
       <c r="P8" t="n">
         <v>4810</v>
@@ -1228,7 +1228,7 @@
         <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="H9" t="n">
         <v>1.09</v>
@@ -1254,7 +1254,7 @@
         <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>20985879985</v>
+        <v>20986985647</v>
       </c>
       <c r="P9" t="n">
         <v>2970</v>
@@ -1314,13 +1314,13 @@
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F10" t="n">
         <v>88</v>
       </c>
       <c r="G10" t="n">
-        <v>942</v>
+        <v>962</v>
       </c>
       <c r="H10" t="n">
         <v>3.81</v>
@@ -1346,7 +1346,7 @@
         <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>236955778030</v>
+        <v>237130404750</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시의 강력한 광통신 섹터 흐름에 기반한 긍정적 전망 제시. 3분기 영업이익 증가 및 외인 순매수 동향을 근거로 상승 추세 예상.</t>
+          <t>미국 증시의 광통신 섹터 강세와 함께 국내에서도 긍정적인 전망이 나옴. 3분기 영업이익 증가 및 수주량 증가 소식이 있으며, 외인 순매수세 유입으로 상승 흐름에 대한 기대감이 높음.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '영업이익', '외인 순매수']</t>
+          <t>['광통신', '영업이익 증가', '외인 순매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="H11" t="n">
         <v>9.390000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>65916757750</v>
+        <v>65947447500</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1498,13 +1498,13 @@
         <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F12" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G12" t="n">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="H12" t="n">
         <v>27.78</v>
@@ -1530,7 +1530,7 @@
         <v>27.73</v>
       </c>
       <c r="O12" t="n">
-        <v>48606619820</v>
+        <v>48610106720</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G13" t="n">
-        <v>1640</v>
+        <v>1623</v>
       </c>
       <c r="H13" t="n">
         <v>46.41</v>
@@ -1622,7 +1622,7 @@
         <v>46.41</v>
       </c>
       <c r="O13" t="n">
-        <v>3469186692750</v>
+        <v>3469449716750</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>증시 전반의 불안정한 흐름 속에서 3분기 110조 영업이익 예상에도 불구하고 주가 하락에 대한 불만 표출. 자사주 매입 및 정치적 이슈 언급.</t>
+          <t>분기 영업이익 100조를 앞두고도 주가 부진. 정치적 이슈와 자사주 매입에 대한 비판이 혼재하며, 실적 기대감에도 불구하고 부정적인 여론이 형성됨.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['영업이익', '자사주 매입', '주가 하락']</t>
+          <t>['영업이익', '주가 부진', '자사주 매입']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="G14" t="n">
-        <v>2035</v>
+        <v>2119</v>
       </c>
       <c r="H14" t="n">
         <v>49.76</v>
@@ -1714,7 +1714,7 @@
         <v>49.77</v>
       </c>
       <c r="O14" t="n">
-        <v>4740625522500</v>
+        <v>4742481853500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 리스크 및 시장 수급 불안정성을 근거로 주가 급락에 대한 강한 불만과 부정적 전망 제시. 주가 조작 의혹 및 국내 증시 소외감 언급.</t>
+          <t>정치적 리스크와 대규모 하락세로 인한 부정적 여론이 지배적. 외인 매도세와 함께 주가 조작 의혹까지 제기되며 투자 심리가 크게 위축됨.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['이재명 리스크', '주가 조작', '수급 불안정']</t>
+          <t>['정치적 리스크', '주가 하락', '외인 매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1780,7 +1780,7 @@
         <v>64</v>
       </c>
       <c r="G15" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H15" t="n">
         <v>0.32</v>
@@ -1806,7 +1806,7 @@
         <v>0.18</v>
       </c>
       <c r="O15" t="n">
-        <v>75491334690</v>
+        <v>75510562290</v>
       </c>
       <c r="P15" t="n">
         <v>29750</v>
